--- a/222/222_222/002_NEN10/条件输入数据表.xlsx
+++ b/222/222_222/002_NEN10/条件输入数据表.xlsx
@@ -2535,8 +2535,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="K1:L1"/>
     <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2597,7 +2597,7 @@
       <c r="C2" s="21" t="inlineStr"/>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>813</t>
         </is>
       </c>
     </row>

--- a/222/222_222/002_NEN10/条件输入数据表.xlsx
+++ b/222/222_222/002_NEN10/条件输入数据表.xlsx
@@ -2535,8 +2535,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2597,7 +2597,7 @@
       <c r="C2" s="21" t="inlineStr"/>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>/</t>
         </is>
       </c>
     </row>
